--- a/datas/ecshop_datas.xlsx
+++ b/datas/ecshop_datas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17090" windowHeight="6880" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="login_data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>title</t>
   </si>
@@ -46,19 +46,22 @@
     <t>正确的用户名正确的密码登录成功</t>
   </si>
   <si>
+    <t>sdfsdf</t>
+  </si>
+  <si>
+    <t>sdf</t>
+  </si>
+  <si>
+    <t>用户名为空密码正确登录失败</t>
+  </si>
+  <si>
+    <t>为空</t>
+  </si>
+  <si>
+    <t>密码为空用户名正确登录失败</t>
+  </si>
+  <si>
     <t>zhangtiedan</t>
-  </si>
-  <si>
-    <t>tiedan</t>
-  </si>
-  <si>
-    <t>用户名为空密码正确登录失败</t>
-  </si>
-  <si>
-    <t>为空</t>
-  </si>
-  <si>
-    <t>密码为空用户名正确登录失败</t>
   </si>
   <si>
     <t>用户名密码不匹配</t>
@@ -1026,10 +1029,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="32.0909090909091" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="19.8888888888889" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5555555555556" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.0925925925926" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1077,7 +1082,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
@@ -1085,16 +1090,16 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1108,17 +1113,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -1126,24 +1131,24 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
         <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -1151,10 +1156,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -1171,7 +1176,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
